--- a/00_output/30_Construction_Inputs.xlsx
+++ b/00_output/30_Construction_Inputs.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,96 +444,6 @@
           <t>multifamily_li</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -551,13 +461,6 @@
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
-        <is>
-          <t>heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
         <is>
           <t>refrigeration_full_size</t>
         </is>
@@ -574,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,96 +506,6 @@
           <t>multifamily_li</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -710,13 +523,6 @@
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
-        <is>
-          <t>heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
         <is>
           <t>refrigeration_full_size</t>
         </is>
@@ -733,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,96 +568,6 @@
           <t>multifamily_li</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -869,13 +585,6 @@
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
-        <is>
-          <t>heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
         <is>
           <t>refrigeration_full_size</t>
         </is>

--- a/00_output/30_Construction_Inputs.xlsx
+++ b/00_output/30_Construction_Inputs.xlsx
@@ -1,36 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_EBBD5B5C9A4F43556FB63783703BBDCB99B3E74E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCEC89F8-BE83-4A52-80B1-CD26A427139B}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New_Construction" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demolition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Renovation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="New_Construction" sheetId="1" r:id="rId1"/>
+    <sheet name="Demolition" sheetId="2" r:id="rId2"/>
+    <sheet name="Demolition_Rate" sheetId="4" r:id="rId3"/>
+    <sheet name="Renovation" sheetId="3" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
+  <si>
+    <t>competition_subgroup</t>
+  </si>
+  <si>
+    <t>single_family</t>
+  </si>
+  <si>
+    <t>multifamily</t>
+  </si>
+  <si>
+    <t>single_family_li</t>
+  </si>
+  <si>
+    <t>multifamily_li</t>
+  </si>
+  <si>
+    <t>heating_cooling_oil_furnace</t>
+  </si>
+  <si>
+    <t>heating_cooling_gas_furnace</t>
+  </si>
+  <si>
+    <t>refrigeration_full_size</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -45,84 +92,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -410,60 +401,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>competition_subgroup</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>single_family</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>multifamily</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>single_family_li</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>multifamily_li</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling_oil_furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling_gas_furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -472,60 +443,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>competition_subgroup</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>single_family</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>multifamily</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>single_family_li</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>multifamily_li</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling_oil_furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling_gas_furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -534,60 +489,138 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56539607-7EA7-4EFC-B4A8-2C4D36C30F87}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="C4" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>competition_subgroup</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>single_family</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>multifamily</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>single_family_li</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>multifamily_li</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling_oil_furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling_gas_furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/00_output/30_Construction_Inputs.xlsx
+++ b/00_output/30_Construction_Inputs.xlsx
@@ -1,83 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_EBBD5B5C9A4F43556FB63783703BBDCB99B3E74E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCEC89F8-BE83-4A52-80B1-CD26A427139B}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="New_Construction" sheetId="1" r:id="rId1"/>
-    <sheet name="Demolition" sheetId="2" r:id="rId2"/>
-    <sheet name="Demolition_Rate" sheetId="4" r:id="rId3"/>
-    <sheet name="Renovation" sheetId="3" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New_Construction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demolition" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Renovation" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
-  <si>
-    <t>competition_subgroup</t>
-  </si>
-  <si>
-    <t>single_family</t>
-  </si>
-  <si>
-    <t>multifamily</t>
-  </si>
-  <si>
-    <t>single_family_li</t>
-  </si>
-  <si>
-    <t>multifamily_li</t>
-  </si>
-  <si>
-    <t>heating_cooling_oil_furnace</t>
-  </si>
-  <si>
-    <t>heating_cooling_gas_furnace</t>
-  </si>
-  <si>
-    <t>refrigeration_full_size</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Linear</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -92,28 +45,84 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -401,40 +410,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>competition_subgroup</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>single_family</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>single_family_li</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>multifamily_li</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>heating_cooling_oil_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>heating_cooling_gas_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>refrigeration_full_size</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -443,44 +472,60 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>competition_subgroup</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>single_family</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>single_family_li</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>multifamily_li</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>heating_cooling_oil_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>heating_cooling_gas_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>refrigeration_full_size</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -489,138 +534,60 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56539607-7EA7-4EFC-B4A8-2C4D36C30F87}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="C3" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="D3" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="E3" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="C4" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="D4" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="E4" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>competition_subgroup</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>single_family</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>single_family_li</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>multifamily_li</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>heating_cooling_oil_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>heating_cooling_gas_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>refrigeration_full_size</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/00_output/30_Construction_Inputs.xlsx
+++ b/00_output/30_Construction_Inputs.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +27,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -44,12 +59,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,58 +458,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>competition_subgroup</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling_oil_furnace</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling_gas_furnace</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -477,58 +687,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>competition_subgroup</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling_oil_furnace</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling_gas_furnace</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -539,58 +916,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>competition_subgroup</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling_oil_furnace</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling_gas_furnace</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/30_Construction_Inputs.xlsx
+++ b/00_output/30_Construction_Inputs.xlsx
@@ -461,7 +461,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -690,7 +690,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -919,7 +919,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
